--- a/Middlesbrough vs Kendall 20251018.xlsx
+++ b/Middlesbrough vs Kendall 20251018.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cex\OneDrive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cex\Desktop\Rugby Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D44B74-26F0-494F-8707-75C91A4C3EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC777267-89B5-4936-AAF6-9C98C51B797F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{9E14DF06-3F9D-43DB-905D-D6717BAB6DD9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9E14DF06-3F9D-43DB-905D-D6717BAB6DD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Middlesbrough" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="76">
   <si>
     <t>Complete Pass</t>
   </si>
@@ -135,9 +135,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>Penalty</t>
-  </si>
-  <si>
     <t>ACA</t>
   </si>
   <si>
@@ -255,7 +252,22 @@
     <t>Kendall</t>
   </si>
   <si>
-    <t>22 Entries</t>
+    <t>22 Entries For</t>
+  </si>
+  <si>
+    <t>22 Entries Against</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>Event</t>
   </si>
 </sst>
 </file>
@@ -648,10 +660,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F828139D-9A59-4A10-B5D4-8BE16B9B29C9}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -671,7 +683,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -710,10 +722,13 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -733,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -774,8 +789,11 @@
       <c r="T2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>9</v>
       </c>
@@ -795,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -836,8 +854,11 @@
       <c r="T3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>7</v>
       </c>
@@ -857,7 +878,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -887,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R4">
         <v>352</v>
@@ -898,8 +919,11 @@
       <c r="T4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>6</v>
       </c>
@@ -919,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -949,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5">
         <v>170</v>
@@ -960,8 +984,11 @@
       <c r="T5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>40</v>
       </c>
@@ -981,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1011,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R6">
         <v>806</v>
@@ -1022,8 +1049,11 @@
       <c r="T6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>21</v>
       </c>
@@ -1043,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1073,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R7">
         <v>533</v>
@@ -1084,8 +1114,11 @@
       <c r="T7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
@@ -1105,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1135,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R8">
         <v>328</v>
@@ -1146,8 +1179,11 @@
       <c r="T8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1167,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1197,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R9">
         <v>577</v>
@@ -1208,8 +1244,11 @@
       <c r="T9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
@@ -1229,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1270,8 +1309,11 @@
       <c r="T10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1291,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1321,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R11">
         <v>162</v>
@@ -1332,8 +1374,11 @@
       <c r="T11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1353,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1383,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R12">
         <v>569</v>
@@ -1394,8 +1439,11 @@
       <c r="T12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1415,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1456,8 +1504,11 @@
       <c r="T13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>8</v>
       </c>
@@ -1477,7 +1528,7 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1507,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R14">
         <v>202</v>
@@ -1518,8 +1569,11 @@
       <c r="T14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>21</v>
       </c>
@@ -1539,7 +1593,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1569,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R15">
         <v>801</v>
@@ -1580,8 +1634,11 @@
       <c r="T15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1601,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1631,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R16">
         <v>372</v>
@@ -1641,6 +1698,9 @@
       </c>
       <c r="T16">
         <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1650,10 +1710,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DC3824-474E-47A4-8F0A-6033B7A91ACE}">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1673,7 +1733,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -1712,10 +1772,13 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>8</v>
       </c>
@@ -1735,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1765,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R2">
         <v>114</v>
@@ -1776,8 +1839,11 @@
       <c r="T2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1788,7 +1854,7 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1797,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1827,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R3">
         <v>235</v>
@@ -1838,8 +1904,11 @@
       <c r="T3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>8</v>
       </c>
@@ -1850,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1859,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1889,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R4">
         <v>352</v>
@@ -1900,8 +1969,11 @@
       <c r="T4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1921,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1962,8 +2034,11 @@
       <c r="T5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>14</v>
       </c>
@@ -1983,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2013,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R6">
         <v>806</v>
@@ -2024,8 +2099,11 @@
       <c r="T6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -2045,7 +2123,7 @@
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -2075,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R7">
         <v>533</v>
@@ -2086,8 +2164,11 @@
       <c r="T7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>8</v>
       </c>
@@ -2107,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2137,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R8">
         <v>328</v>
@@ -2148,8 +2229,11 @@
       <c r="T8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2169,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2199,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R9">
         <v>577</v>
@@ -2210,8 +2294,11 @@
       <c r="T9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>6</v>
       </c>
@@ -2231,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2261,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R10">
         <v>155</v>
@@ -2272,8 +2359,11 @@
       <c r="T10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2293,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2323,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R11">
         <v>162</v>
@@ -2334,8 +2424,11 @@
       <c r="T11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>12</v>
       </c>
@@ -2346,7 +2439,7 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -2355,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2385,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R12">
         <v>569</v>
@@ -2396,8 +2489,11 @@
       <c r="T12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
@@ -2417,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -2447,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R13">
         <v>137</v>
@@ -2458,8 +2554,11 @@
       <c r="T13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4</v>
       </c>
@@ -2467,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -2479,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -2509,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R14">
         <v>202</v>
@@ -2520,8 +2619,11 @@
       <c r="T14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2541,7 +2643,7 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -2571,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R15">
         <v>801</v>
@@ -2582,8 +2684,11 @@
       <c r="T15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>12</v>
       </c>
@@ -2603,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -2633,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R16">
         <v>372</v>
@@ -2643,6 +2748,9 @@
       </c>
       <c r="T16">
         <v>1</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2714,7 +2822,7 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U1" s="1"/>
     </row>
@@ -2774,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
@@ -2824,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R3">
         <v>60</v>
@@ -2833,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -2886,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -2895,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
@@ -2906,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -2954,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -3001,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R6">
         <v>25</v>
@@ -3010,7 +3118,7 @@
         <v>5</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -3057,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R7">
         <v>53</v>
@@ -3066,7 +3174,7 @@
         <v>2</v>
       </c>
       <c r="T7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -3077,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3122,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -3169,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R9">
         <v>31</v>
@@ -3178,7 +3286,7 @@
         <v>4</v>
       </c>
       <c r="T9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -3225,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R10">
         <v>27</v>
@@ -3234,7 +3342,7 @@
         <v>3</v>
       </c>
       <c r="T10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
@@ -3281,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11">
         <v>6</v>
@@ -3290,7 +3398,7 @@
         <v>7</v>
       </c>
       <c r="T11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -3337,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R12">
         <v>32</v>
@@ -3346,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
@@ -3393,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R13">
         <v>106</v>
@@ -3402,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="T13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
@@ -3449,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R14">
         <v>71</v>
@@ -3458,7 +3566,7 @@
         <v>3</v>
       </c>
       <c r="T14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
@@ -3514,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
@@ -3561,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R16">
         <v>15</v>
@@ -3570,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="T16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
@@ -3626,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.35">
@@ -3682,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -3729,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R19">
         <v>79</v>
@@ -3738,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="T19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.35">
@@ -3794,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="T20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.35">
@@ -3850,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.35">
@@ -3897,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R22">
         <v>25</v>
@@ -3906,7 +4014,7 @@
         <v>3</v>
       </c>
       <c r="T22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.35">
@@ -3962,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4034,7 +4142,7 @@
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
@@ -4087,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R2">
         <v>114</v>
@@ -4096,7 +4204,7 @@
         <v>10</v>
       </c>
       <c r="T2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
@@ -4158,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -4220,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -4273,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R5">
         <v>114</v>
@@ -4282,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="T5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
@@ -4344,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
@@ -4403,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -4453,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R8">
         <v>68</v>
@@ -4462,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
@@ -4521,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
@@ -4580,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -4639,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -4698,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -4757,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -4771,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4816,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
@@ -4875,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -4934,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
@@ -4984,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R17">
         <v>59</v>
@@ -4993,7 +5101,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
@@ -5004,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -5043,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R18">
         <v>97</v>
@@ -5052,7 +5160,7 @@
         <v>3</v>
       </c>
       <c r="T18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
@@ -5111,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.35">
@@ -5170,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.35">
@@ -5220,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R21">
         <v>36</v>
@@ -5229,7 +5337,7 @@
         <v>4</v>
       </c>
       <c r="T21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.35">
@@ -5288,7 +5396,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
@@ -5338,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R23">
         <v>4</v>
@@ -5347,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="T23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
